--- a/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
+++ b/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EXCL. sales tax, with staffing and the service charge included and the voluntary gratuity left out: the price per guest you quote before tax. Price per guest incl. sales tax = this value × (1 + your sales tax rate). The example sits inside the per-guest range in the benchmarks table on the "Instructions" tab (Kit estimate); the Pricing Calculator in this kit builds the price per guest for each service style.</t>
+          <t>EXCL. sales tax, with staffing and the service charge included and the voluntary gratuity left out: the price per guest you quote before tax. Price per guest incl. sales tax = this value × (1 + your sales tax rate). The example sits inside the per-guest range in the benchmarks table on the "Instructions" tab (Kit estimate); the Pricing Calculator builds a quote per service style; to bring it here, divide its subtotal plus the service charge you keep by the billable guests (its own price per guest excludes the service charge).</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FICA (Social Security 6.2% + Medicare 1.45%) + federal and state unemployment taxes (FUTA / SUTA) + workers' comp. About 10% in total: adjust it to your state and your insurance carrier</t>
+          <t>FICA (Social Security 6.2% + Medicare 1.45%) + federal and state unemployment taxes (FUTA / SUTA) + workers' comp. The example uses a lean 10% with no benefits; the benchmarks table on "Instructions" gives 15-30% with benefits. Ask your payroll provider and carrier for your rate.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Example rate: state + local sales tax combined. It varies widely by state and city: look up yours. UK: 20% VAT on hot food and dine-in</t>
+          <t>Example rate: state + local sales tax combined. It varies widely by state and city: look up yours. UK: 20% VAT applies to catering for events and functions (VAT Notice 709/1)</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>Minimum cushion of the plan above break-even (plan ÷ break-even − 1). The drop you can absorb is 1 − break-even ÷ plan: a 15% cushion lets events fall by about 13% before costs stop being covered</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
     <row r="15">
       <c r="A15" s="28" t="inlineStr">
         <is>
-          <t>Health plan review (only if you lease your own kitchen)</t>
+          <t>Health permit plan / SOP review</t>
         </is>
       </c>
       <c r="B15" s="49" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="D15" s="28" t="inlineStr">
         <is>
-          <t>Only if you lease your own kitchen: most health departments require a plan review with drawings of the layout and workflow. If you cook in a permitted commissary you usually skip it, so set this line to 0.</t>
+          <t>Many counties review a caterer's written operating procedures before issuing the permit and charge a plan review fee (one California county does: eldoradocounty.ca.gov). If you lease your own kitchen, expect a full plan review with layout drawings, which costs more.</t>
         </is>
       </c>
       <c r="E15" s="31" t="inlineStr">
@@ -2065,8 +2065,8 @@
         <v>0.013480504494400199</v>
       </c>
       <c r="D21" s="28" t="str">
-        <f>IFERROR(""&amp;TEXT('0. Assumptions'!$B$25,"0")&amp;IF('0. Assumptions'!$B$25=1," month"," months")&amp;" of rent, from ""0. Assumptions"". Refundable when the lease ends: it is not depreciated and carries no tax","")</f>
-        <v>1 month of rent, from "0. Assumptions". Refundable when the lease ends: it is not depreciated and carries no tax</v>
+        <f>IFERROR(""&amp;TEXT('0. Assumptions'!$B$25,"0")&amp;IF('0. Assumptions'!$B$25=1," month"," months")&amp;" of rent, from ""0. Assumptions"". Refundable when the commissary agreement ends: it is not depreciated and carries no tax","")</f>
+        <v>1 month of rent, from "0. Assumptions". Refundable when the commissary agreement ends: it is not depreciated and carries no tax</v>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
@@ -2755,8 +2755,8 @@
         <v>0.03</v>
       </c>
       <c r="F18" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales. It is a VARIABLE cost: it moves with revenue, so it cannot sit in fixed costs","")</f>
-        <v>At 3% of sales. It is a VARIABLE cost: it moves with revenue, so it cannot sit in fixed costs</v>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales: van fuel for each trip to the venues plus a cushion for unbudgeted running costs. It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (van maintenance and inspections are in row 27)","")</f>
+        <v>At 3% of sales: van fuel for each trip to the venues plus a cushion for unbudgeted running costs. It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (van maintenance and inspections are in row 27)</v>
       </c>
       <c r="G18" s="68">
         <f>IFERROR(IF(B9="","",'0. Assumptions'!$B$41),"")</f>
@@ -2991,7 +2991,7 @@
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>Van fuel, maintenance and inspections</t>
+          <t>Van maintenance, repairs and inspections</t>
         </is>
       </c>
       <c r="B27" s="49" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Ceiling for the blended cost of goods sold plus disposables: kit benchmark (editable estimate), based on the 28-35% food cost range for caterers in the benchmarks table.</t>
+          <t>Ceiling for food + beverage cost of goods (disposables have their own line): kit benchmark (editable estimate), based on the 28-35% food cost range for caterers in the benchmarks table.</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far the plan sits above the cash break-even (plan ÷ break-even − 1); the drop you can absorb is 1 − break-even ÷ plan. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="194.5" customHeight="1">
+    <row r="24" ht="150" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>The gross pay, employer payroll taxes, monthly cost and annual cost columns are TOTALS for the row: the event staff row covers all the people in it. Event staff (servers, bartenders, attendants) are budgeted as hourly W-2 employees with employer payroll taxes and workers' comp: paying them as 1099 contractors is a misclassification risk (FLSA economic-reality test; California AB5 presumes employment). The payroll tax rate and the number of pay periods are in the "0. Assumptions" tab.</t>
+          <t>Columns D-G are TOTALS for the row: the event staff row covers all its people. Event staff (servers, bartenders, attendants) are hourly W-2 employees with payroll taxes and workers' comp; paying them as 1099 contractors is a misclassification risk (FLSA; California AB5). Tax rate and pay periods: "0. Assumptions".</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="58" t="inlineStr">
         <is>
-          <t>Generator and fuel</t>
+          <t>Generator and burner fuel</t>
         </is>
       </c>
       <c r="B43" s="58" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
+    <row r="66" ht="74.75" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
           <t>Startup investment</t>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>With a shared kitchen; $250K+ if you build your own. Your total depends mostly on the van and the equipment you choose.</t>
+          <t>With a shared kitchen; $250K+ if you build your own. Your total depends mostly on the van and the equipment you choose. The example ($107,200 before working capital) sits above this range because it buys a refrigerated van ($41,000 with its unit) and its own serving equipment.</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="O5" s="28" t="inlineStr">
         <is>
-          <t>Share of the year's events in each month (adds up to 100%). Month 1 = your opening month: the example opens in March, so it starts with spring weddings and peaks in October and December (holiday parties); to open in another month, rotate the row. Deposits (25-50% when the contract is signed) are not modeled: they make your real cash flow better than this sheet.</t>
+          <t>Share of the year's events per month (100% in total). Month 1 = opening month (March in the example): rotate the row.</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
+++ b/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
@@ -2113,7 +2113,7 @@
         <v>0.025343348449472374</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (used refrigerated van, van upfit, van refrigeration unit, commissary storage fit-out and health plan review), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (used refrigerated van, van upfit, van refrigeration unit, commissary storage fit-out and health plan review), not of the whole block: the other items are left out. No lender funds a build-out without "&amp;"a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (used refrigerated van, van upfit, van refrigeration unit, commissary storage fit-out and health plan review), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2271,7 +2271,7 @@
         <v>15054.285714285714</v>
       </c>
       <c r="D33" s="37" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits, opening inventory, website, photography and launch marketing, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits, opening inventory, website, photography and launch marketing, the commissary deposit, pre-opening commissary rent and the working capital "&amp;"reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits, opening inventory, website, photography and launch marketing, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to 100753 of the 185453 total investment.</v>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
+++ b/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
@@ -8239,7 +8239,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>

--- a/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
+++ b/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
@@ -2113,7 +2113,7 @@
         <v>0.025343348449472374</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (used refrigerated van, van upfit, van refrigeration unit, commissary storage fit-out and health plan review), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (used refrigerated van, van upfit, van refrigeration unit, commissary storage fit-out and health plan review), not of the whole block: the other items are left out. No lender funds a build-out without "&amp;"a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (used refrigerated van, van upfit, van refrigeration unit, commissary storage fit-out and health plan review), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2271,7 +2271,7 @@
         <v>15054.285714285714</v>
       </c>
       <c r="D33" s="37" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits, opening inventory, website, photography and launch marketing, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits, opening inventory, website, photography and launch marketing, the commissary deposit, pre-opening commissary rent and the working capital "&amp;"reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits, opening inventory, website, photography and launch marketing, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to 100753 of the 185453 total investment.</v>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>

--- a/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
+++ b/astro-site/public/dl/catering-business-plan/catering-financial-projections.xlsx
@@ -8236,7 +8236,7 @@
       <c r="N33" s="28" t="n"/>
       <c r="O33" s="28" t="n"/>
     </row>
-    <row r="34" ht="134.75" customHeight="1">
+    <row r="34" ht="149.5" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
           <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
